--- a/jira_export_2026-07-25.xlsx
+++ b/jira_export_2026-07-25.xlsx
@@ -14871,13 +14871,13 @@
         <v>269055</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>196258</v>
+        <v>183736</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>21917</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>14855</v>
+        <v>27377</v>
       </c>
     </row>
     <row r="6">
@@ -14921,13 +14921,13 @@
         <v>157177</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>98144</v>
+        <v>85622</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>11857</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>11151</v>
+        <v>23673</v>
       </c>
     </row>
   </sheetData>
